--- a/artfynd/A 36940-2025 artfynd.xlsx
+++ b/artfynd/A 36940-2025 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91970087</v>
+        <v>97044355</v>
       </c>
       <c r="B2" t="n">
-        <v>105726</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231645</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Växeltandsfibbla</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium dentifolium</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(C. G. Westerl.) Johanss. &amp; Sam.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>600 m NNO Kanaberg, Sm</t>
+          <t>KÄTTILHULT 1:6, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560179.5553006452</v>
+        <v>560258</v>
       </c>
       <c r="R2" t="n">
-        <v>6265953.655312026</v>
+        <v>6266047</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,91 +758,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Eric Lundén</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eric Lundén</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eric Lundén</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97044355</v>
+        <v>91970087</v>
       </c>
       <c r="B3" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>231645</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Växeltandsfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hieracium dentifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(C. G. Westerl.) Johanss. &amp; Sam.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄTTILHULT 1:6, Sm</t>
+          <t>600 m NNO Kanaberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560257.7984196137</v>
+        <v>560180</v>
       </c>
       <c r="R3" t="n">
-        <v>6266046.863528582</v>
+        <v>6265954</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +856,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Eric Lundén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Eric Lundén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 36940-2025 artfynd.xlsx
+++ b/artfynd/A 36940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97044355</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91970087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>